--- a/tools/importer/reports/import-case-study.report.xlsx
+++ b/tools/importer/reports/import-case-study.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
   <si>
     <t>_reportFile</t>
   </si>
@@ -103,7 +103,7 @@
     <t>site/us/en/about/case-studies-customer-stories/nestle.report.json</t>
   </si>
   <si>
-    <t>[]</t>
+    <t>["hero","columns","cards","cards","cards","cards"]</t>
   </si>
   <si>
     <t>site/us/en/about/case-studies-customer-stories/nestle</t>
@@ -112,7 +112,7 @@
     <t>case-study</t>
   </si>
   <si>
-    <t>2026-04-15T19:01:16.816Z</t>
+    <t>2026-04-15T19:43:44.173Z</t>
   </si>
   <si>
     <t>Nestlé and Cisco SD-WAN Case Study - Cisco</t>
@@ -145,10 +145,13 @@
     <t>site/us/en/about/why-cisco/mclaren-racing.report.json</t>
   </si>
   <si>
+    <t>["columns"]</t>
+  </si>
+  <si>
     <t>site/us/en/about/why-cisco/mclaren-racing</t>
   </si>
   <si>
-    <t>2026-04-15T19:01:23.727Z</t>
+    <t>2026-04-15T19:43:51.563Z</t>
   </si>
   <si>
     <t>Cisco powers the McLaren F1 Team - Cisco</t>
@@ -752,10 +755,10 @@
         <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
@@ -764,65 +767,65 @@
         <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
